--- a/outputs/hospital_summary.xlsx
+++ b/outputs/hospital_summary.xlsx
@@ -448,10 +448,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D2" t="n">
-        <v>1.040600891381073</v>
+        <v>2.656568341780027</v>
       </c>
     </row>
     <row r="3">
@@ -464,10 +464,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D3" t="n">
-        <v>1.034825403152413</v>
+        <v>1.626169978748408</v>
       </c>
     </row>
     <row r="4">
@@ -480,10 +480,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D4" t="n">
-        <v>2.726330288530827</v>
+        <v>2.658174185586282</v>
       </c>
     </row>
     <row r="5">
@@ -496,10 +496,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D5" t="n">
-        <v>2.737224369372361</v>
+        <v>2.644868791186249</v>
       </c>
     </row>
     <row r="6">
@@ -512,10 +512,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D6" t="n">
-        <v>1.031567295745109</v>
+        <v>1.552249672337743</v>
       </c>
     </row>
     <row r="7">
@@ -528,10 +528,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D7" t="n">
-        <v>1.037245808217465</v>
+        <v>1.529473512579836</v>
       </c>
     </row>
     <row r="8">
@@ -544,10 +544,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D8" t="n">
-        <v>1.040828043052919</v>
+        <v>1.425533930090847</v>
       </c>
     </row>
     <row r="9">
@@ -560,10 +560,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D9" t="n">
-        <v>1.053343065668939</v>
+        <v>1.71972179717966</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D10" t="n">
-        <v>1.061464707124177</v>
+        <v>1.568408043534562</v>
       </c>
     </row>
     <row r="11">
@@ -592,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D11" t="n">
-        <v>2.799126818586559</v>
+        <v>2.919950864332946</v>
       </c>
     </row>
     <row r="12">
@@ -608,10 +608,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D12" t="n">
-        <v>1.045901207627511</v>
+        <v>1.851417341810201</v>
       </c>
     </row>
     <row r="13">
@@ -624,10 +624,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D13" t="n">
-        <v>1.038777372150877</v>
+        <v>1.525522937702212</v>
       </c>
     </row>
     <row r="14">
@@ -640,10 +640,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D14" t="n">
-        <v>1.054832954767649</v>
+        <v>1.463574363205554</v>
       </c>
     </row>
     <row r="15">
@@ -656,10 +656,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D15" t="n">
-        <v>1.032600791141349</v>
+        <v>1.528756879804177</v>
       </c>
     </row>
     <row r="16">
@@ -672,10 +672,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1.734889563684189</v>
+        <v>2.097301376371893</v>
       </c>
       <c r="D16" t="n">
-        <v>1.014115517047819</v>
+        <v>1.115132741575543</v>
       </c>
     </row>
     <row r="17">
@@ -688,10 +688,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1.734889563684189</v>
+        <v>2.097301376371893</v>
       </c>
       <c r="D17" t="n">
-        <v>1.008926309595771</v>
+        <v>1.088438685880915</v>
       </c>
     </row>
     <row r="18">
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.734889563684189</v>
+        <v>2.097301376371893</v>
       </c>
       <c r="D18" t="n">
-        <v>1.008771876947411</v>
+        <v>1.059760659651125</v>
       </c>
     </row>
     <row r="19">
@@ -720,10 +720,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.734889563684189</v>
+        <v>2.097301376371893</v>
       </c>
       <c r="D19" t="n">
-        <v>1.105649607582305</v>
+        <v>2.661983786884838</v>
       </c>
     </row>
     <row r="20">
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.734889563684189</v>
+        <v>2.097301376371893</v>
       </c>
       <c r="D20" t="n">
-        <v>1.00808036883536</v>
+        <v>1.209962458228269</v>
       </c>
     </row>
     <row r="21">
@@ -752,10 +752,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1.734889563684189</v>
+        <v>2.097301376371893</v>
       </c>
       <c r="D21" t="n">
-        <v>1.006318621750094</v>
+        <v>1.121899145189923</v>
       </c>
     </row>
     <row r="22">
@@ -768,10 +768,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1.734889563684189</v>
+        <v>2.097301376371893</v>
       </c>
       <c r="D22" t="n">
-        <v>1.009253636334949</v>
+        <v>1.336146388341593</v>
       </c>
     </row>
     <row r="23">
@@ -784,10 +784,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1.734889563684189</v>
+        <v>2.097301376371893</v>
       </c>
       <c r="D23" t="n">
-        <v>1.008455629559833</v>
+        <v>1.344641176256636</v>
       </c>
     </row>
     <row r="24">
@@ -800,10 +800,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.734889563684189</v>
+        <v>2.097301376371893</v>
       </c>
       <c r="D24" t="n">
-        <v>1.009537700188205</v>
+        <v>2.250343850974021</v>
       </c>
     </row>
     <row r="25">
@@ -816,10 +816,10 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D25" t="n">
-        <v>2.381992804642781</v>
+        <v>2.620584077463712</v>
       </c>
     </row>
     <row r="26">
@@ -832,10 +832,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D26" t="n">
-        <v>1.058621041238492</v>
+        <v>1.840465245966701</v>
       </c>
     </row>
     <row r="27">
@@ -848,10 +848,10 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D27" t="n">
-        <v>1.032675144844425</v>
+        <v>1.367403200748503</v>
       </c>
     </row>
     <row r="28">
@@ -864,10 +864,10 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>1.757003084629749</v>
+        <v>2.129176810607219</v>
       </c>
       <c r="D28" t="n">
-        <v>1.023460397532901</v>
+        <v>2.440425806210527</v>
       </c>
     </row>
     <row r="29">
@@ -880,10 +880,10 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>1.757003084629749</v>
+        <v>2.129176810607219</v>
       </c>
       <c r="D29" t="n">
-        <v>2.515702928388074</v>
+        <v>2.585849691534151</v>
       </c>
     </row>
     <row r="30">
@@ -896,10 +896,10 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>1.724931380485363</v>
+        <v>2.095011898858255</v>
       </c>
       <c r="D30" t="n">
-        <v>2.859125441136113</v>
+        <v>2.619342497575487</v>
       </c>
     </row>
     <row r="31">
@@ -912,10 +912,10 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1.724931380485363</v>
+        <v>2.095011898858255</v>
       </c>
       <c r="D31" t="n">
-        <v>1.012343232454409</v>
+        <v>1.546449123081917</v>
       </c>
     </row>
     <row r="32">
@@ -928,10 +928,10 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>1.734889563684189</v>
+        <v>2.097301376371893</v>
       </c>
       <c r="D32" t="n">
-        <v>1.017660978412494</v>
+        <v>1.276945231227929</v>
       </c>
     </row>
     <row r="33">
@@ -944,10 +944,10 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D33" t="n">
-        <v>1.061481472103344</v>
+        <v>1.377879708063598</v>
       </c>
     </row>
     <row r="34">
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D34" t="n">
-        <v>1.052252746266336</v>
+        <v>1.60626603182629</v>
       </c>
     </row>
     <row r="35">
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D35" t="n">
-        <v>1.034044335839531</v>
+        <v>1.557581500794853</v>
       </c>
     </row>
     <row r="36">
@@ -992,10 +992,10 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D36" t="n">
-        <v>1.094086429687842</v>
+        <v>2.81880615282618</v>
       </c>
     </row>
     <row r="37">
@@ -1008,10 +1008,10 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D37" t="n">
-        <v>1.086951517157469</v>
+        <v>2.866860854733831</v>
       </c>
     </row>
     <row r="38">
@@ -1024,10 +1024,10 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>2.186164361537113</v>
+        <v>2.513649765762667</v>
       </c>
       <c r="D38" t="n">
-        <v>1.042457863985735</v>
+        <v>1.678878684551861</v>
       </c>
     </row>
     <row r="39">
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>1.465504937817449</v>
+        <v>1.784987249253573</v>
       </c>
       <c r="D39" t="n">
-        <v>1.036424259476232</v>
+        <v>1.101106717231545</v>
       </c>
     </row>
     <row r="40">
@@ -1056,10 +1056,10 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>1.465504937817449</v>
+        <v>1.784987249253573</v>
       </c>
       <c r="D40" t="n">
-        <v>1.179450395075664</v>
+        <v>1.907913025267788</v>
       </c>
     </row>
     <row r="41">
@@ -1072,10 +1072,10 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>1.724931380485363</v>
+        <v>2.095011898858255</v>
       </c>
       <c r="D41" t="n">
-        <v>1.003623812785898</v>
+        <v>1.221267013687321</v>
       </c>
     </row>
     <row r="42">
@@ -1088,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>1.724931380485363</v>
+        <v>2.095011898858255</v>
       </c>
       <c r="D42" t="n">
-        <v>1.026343474624335</v>
+        <v>1.058487207446726</v>
       </c>
     </row>
     <row r="43">
@@ -1104,10 +1104,10 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>1.757003084629749</v>
+        <v>2.129176810607219</v>
       </c>
       <c r="D43" t="n">
-        <v>1.00748854606062</v>
+        <v>1.096386466821318</v>
       </c>
     </row>
     <row r="44">
@@ -1120,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>1.757003084629749</v>
+        <v>2.129176810607219</v>
       </c>
       <c r="D44" t="n">
-        <v>1.008608991964808</v>
+        <v>1.049008416937481</v>
       </c>
     </row>
     <row r="45">
@@ -1136,10 +1136,10 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>1.757003084629749</v>
+        <v>2.129176810607219</v>
       </c>
       <c r="D45" t="n">
-        <v>1.006523196192527</v>
+        <v>1.029786054152452</v>
       </c>
     </row>
     <row r="46">
@@ -1152,10 +1152,10 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>1.734889563684189</v>
+        <v>2.097301376371893</v>
       </c>
       <c r="D46" t="n">
-        <v>1.053218296980876</v>
+        <v>1.086092081965878</v>
       </c>
     </row>
     <row r="47">
@@ -1168,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>1.734889563684189</v>
+        <v>2.097301376371893</v>
       </c>
       <c r="D47" t="n">
-        <v>1.021974418132583</v>
+        <v>1.276553352004134</v>
       </c>
     </row>
     <row r="48">
@@ -1184,10 +1184,10 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>1.734889563684189</v>
+        <v>2.097301376371893</v>
       </c>
       <c r="D48" t="n">
-        <v>2.704973656006316</v>
+        <v>2.744553245101073</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hospital_summary.xlsx
+++ b/outputs/hospital_summary.xlsx
@@ -448,10 +448,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2.513649765762667</v>
+        <v>2.177682639126641</v>
       </c>
       <c r="D2" t="n">
-        <v>2.656568341780027</v>
+        <v>1.071061827129748</v>
       </c>
     </row>
     <row r="3">
@@ -464,10 +464,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>2.513649765762667</v>
+        <v>2.195428426552186</v>
       </c>
       <c r="D3" t="n">
-        <v>1.626169978748408</v>
+        <v>1.044501294258234</v>
       </c>
     </row>
     <row r="4">
@@ -480,10 +480,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>2.513649765762667</v>
+        <v>2.218541825787641</v>
       </c>
       <c r="D4" t="n">
-        <v>2.658174185586282</v>
+        <v>1.374854953355303</v>
       </c>
     </row>
     <row r="5">
@@ -496,10 +496,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>2.513649765762667</v>
+        <v>2.278616178635162</v>
       </c>
       <c r="D5" t="n">
-        <v>2.644868791186249</v>
+        <v>1.090523476197044</v>
       </c>
     </row>
     <row r="6">
@@ -512,10 +512,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>2.513649765762667</v>
+        <v>2.238810739616622</v>
       </c>
       <c r="D6" t="n">
-        <v>1.552249672337743</v>
+        <v>1.060812748256447</v>
       </c>
     </row>
     <row r="7">
@@ -528,10 +528,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2.513649765762667</v>
+        <v>2.190493328687032</v>
       </c>
       <c r="D7" t="n">
-        <v>1.529473512579836</v>
+        <v>1.032544991596828</v>
       </c>
     </row>
     <row r="8">
@@ -544,10 +544,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2.513649765762667</v>
+        <v>2.107468634740377</v>
       </c>
       <c r="D8" t="n">
-        <v>1.425533930090847</v>
+        <v>1.019508968145117</v>
       </c>
     </row>
     <row r="9">
@@ -560,10 +560,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2.513649765762667</v>
+        <v>2.194401309340316</v>
       </c>
       <c r="D9" t="n">
-        <v>1.71972179717966</v>
+        <v>1.039482959585712</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.513649765762667</v>
+        <v>2.127220584661621</v>
       </c>
       <c r="D10" t="n">
-        <v>1.568408043534562</v>
+        <v>1.041891539182229</v>
       </c>
     </row>
     <row r="11">
@@ -592,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2.513649765762667</v>
+        <v>2.31304270891115</v>
       </c>
       <c r="D11" t="n">
-        <v>2.919950864332946</v>
+        <v>2.882911465181623</v>
       </c>
     </row>
     <row r="12">
@@ -608,10 +608,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2.513649765762667</v>
+        <v>2.147167199272698</v>
       </c>
       <c r="D12" t="n">
-        <v>1.851417341810201</v>
+        <v>1.054873544966977</v>
       </c>
     </row>
     <row r="13">
@@ -624,10 +624,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.513649765762667</v>
+        <v>2.203381001286713</v>
       </c>
       <c r="D13" t="n">
-        <v>1.525522937702212</v>
+        <v>1.034065521272477</v>
       </c>
     </row>
     <row r="14">
@@ -640,10 +640,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.513649765762667</v>
+        <v>2.173098848687933</v>
       </c>
       <c r="D14" t="n">
-        <v>1.463574363205554</v>
+        <v>1.036553796011563</v>
       </c>
     </row>
     <row r="15">
@@ -656,10 +656,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2.513649765762667</v>
+        <v>2.107121097563563</v>
       </c>
       <c r="D15" t="n">
-        <v>1.528756879804177</v>
+        <v>1.014988050878614</v>
       </c>
     </row>
     <row r="16">
@@ -672,10 +672,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2.097301376371893</v>
+        <v>1.814894809625688</v>
       </c>
       <c r="D16" t="n">
-        <v>1.115132741575543</v>
+        <v>1.001827626050436</v>
       </c>
     </row>
     <row r="17">
@@ -688,10 +688,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2.097301376371893</v>
+        <v>1.7141611724479</v>
       </c>
       <c r="D17" t="n">
-        <v>1.088438685880915</v>
+        <v>1.00210770601287</v>
       </c>
     </row>
     <row r="18">
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2.097301376371893</v>
+        <v>1.626883503077782</v>
       </c>
       <c r="D18" t="n">
-        <v>1.059760659651125</v>
+        <v>1.00075718223853</v>
       </c>
     </row>
     <row r="19">
@@ -720,10 +720,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>2.097301376371893</v>
+        <v>1.954744738438457</v>
       </c>
       <c r="D19" t="n">
-        <v>2.661983786884838</v>
+        <v>1.007149157155526</v>
       </c>
     </row>
     <row r="20">
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2.097301376371893</v>
+        <v>1.575073186713787</v>
       </c>
       <c r="D20" t="n">
-        <v>1.209962458228269</v>
+        <v>1.002220938875395</v>
       </c>
     </row>
     <row r="21">
@@ -752,10 +752,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>2.097301376371893</v>
+        <v>1.391370579658687</v>
       </c>
       <c r="D21" t="n">
-        <v>1.121899145189923</v>
+        <v>1.00091003512941</v>
       </c>
     </row>
     <row r="22">
@@ -768,10 +768,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>2.097301376371893</v>
+        <v>1.583365492283237</v>
       </c>
       <c r="D22" t="n">
-        <v>1.336146388341593</v>
+        <v>1.00992368922174</v>
       </c>
     </row>
     <row r="23">
@@ -784,10 +784,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2.097301376371893</v>
+        <v>1.580578806924005</v>
       </c>
       <c r="D23" t="n">
-        <v>1.344641176256636</v>
+        <v>1.006505776717569</v>
       </c>
     </row>
     <row r="24">
@@ -800,10 +800,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2.097301376371893</v>
+        <v>1.585476855519401</v>
       </c>
       <c r="D24" t="n">
-        <v>2.250343850974021</v>
+        <v>1.005087488100988</v>
       </c>
     </row>
     <row r="25">
@@ -816,10 +816,10 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>2.513649765762667</v>
+        <v>2.20509018218745</v>
       </c>
       <c r="D25" t="n">
-        <v>2.620584077463712</v>
+        <v>2.315267798700703</v>
       </c>
     </row>
     <row r="26">
@@ -832,10 +832,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>2.513649765762667</v>
+        <v>2.091743962646496</v>
       </c>
       <c r="D26" t="n">
-        <v>1.840465245966701</v>
+        <v>1.048059596489599</v>
       </c>
     </row>
     <row r="27">
@@ -848,10 +848,10 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>2.513649765762667</v>
+        <v>2.04837127749825</v>
       </c>
       <c r="D27" t="n">
-        <v>1.367403200748503</v>
+        <v>1.05166379701486</v>
       </c>
     </row>
     <row r="28">
@@ -864,10 +864,10 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>2.129176810607219</v>
+        <v>2.015814089069948</v>
       </c>
       <c r="D28" t="n">
-        <v>2.440425806210527</v>
+        <v>1.020600311144518</v>
       </c>
     </row>
     <row r="29">
@@ -880,10 +880,10 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>2.129176810607219</v>
+        <v>2.045293897884996</v>
       </c>
       <c r="D29" t="n">
-        <v>2.585849691534151</v>
+        <v>2.564026113922534</v>
       </c>
     </row>
     <row r="30">
@@ -896,10 +896,10 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>2.095011898858255</v>
+        <v>2.013159770003356</v>
       </c>
       <c r="D30" t="n">
-        <v>2.619342497575487</v>
+        <v>2.428267768300765</v>
       </c>
     </row>
     <row r="31">
@@ -912,10 +912,10 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>2.095011898858255</v>
+        <v>1.987378255294497</v>
       </c>
       <c r="D31" t="n">
-        <v>1.546449123081917</v>
+        <v>1.019161279942785</v>
       </c>
     </row>
     <row r="32">
@@ -928,10 +928,10 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2.097301376371893</v>
+        <v>1.934547685258584</v>
       </c>
       <c r="D32" t="n">
-        <v>1.276945231227929</v>
+        <v>1.00639876927893</v>
       </c>
     </row>
     <row r="33">
@@ -944,10 +944,10 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>2.513649765762667</v>
+        <v>1.971456457640082</v>
       </c>
       <c r="D33" t="n">
-        <v>1.377879708063598</v>
+        <v>1.006434709134189</v>
       </c>
     </row>
     <row r="34">
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2.513649765762667</v>
+        <v>2.205926716882059</v>
       </c>
       <c r="D34" t="n">
-        <v>1.60626603182629</v>
+        <v>1.062205042722092</v>
       </c>
     </row>
     <row r="35">
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>2.513649765762667</v>
+        <v>2.256166084887665</v>
       </c>
       <c r="D35" t="n">
-        <v>1.557581500794853</v>
+        <v>1.052992138865038</v>
       </c>
     </row>
     <row r="36">
@@ -992,10 +992,10 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>2.513649765762667</v>
+        <v>2.2757784853328</v>
       </c>
       <c r="D36" t="n">
-        <v>2.81880615282618</v>
+        <v>1.058271182087071</v>
       </c>
     </row>
     <row r="37">
@@ -1008,10 +1008,10 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>2.513649765762667</v>
+        <v>2.321728551842823</v>
       </c>
       <c r="D37" t="n">
-        <v>2.866860854733831</v>
+        <v>2.830131163104121</v>
       </c>
     </row>
     <row r="38">
@@ -1024,10 +1024,10 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>2.513649765762667</v>
+        <v>2.079677061441526</v>
       </c>
       <c r="D38" t="n">
-        <v>1.678878684551861</v>
+        <v>1.149784091983938</v>
       </c>
     </row>
     <row r="39">
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>1.784987249253573</v>
+        <v>1.100411368044227</v>
       </c>
       <c r="D39" t="n">
-        <v>1.101106717231545</v>
+        <v>1.000592876951873</v>
       </c>
     </row>
     <row r="40">
@@ -1056,10 +1056,10 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>1.784987249253573</v>
+        <v>1.713370735726198</v>
       </c>
       <c r="D40" t="n">
-        <v>1.907913025267788</v>
+        <v>1.070004670929269</v>
       </c>
     </row>
     <row r="41">
@@ -1072,10 +1072,10 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>2.095011898858255</v>
+        <v>1.403786503688199</v>
       </c>
       <c r="D41" t="n">
-        <v>1.221267013687321</v>
+        <v>1.006800811502852</v>
       </c>
     </row>
     <row r="42">
@@ -1088,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>2.095011898858255</v>
+        <v>1.039299999265725</v>
       </c>
       <c r="D42" t="n">
-        <v>1.058487207446726</v>
+        <v>1.000754833446681</v>
       </c>
     </row>
     <row r="43">
@@ -1104,10 +1104,10 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>2.129176810607219</v>
+        <v>1.3385364430736</v>
       </c>
       <c r="D43" t="n">
-        <v>1.096386466821318</v>
+        <v>1.007827866504861</v>
       </c>
     </row>
     <row r="44">
@@ -1120,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>2.129176810607219</v>
+        <v>1.218705354107325</v>
       </c>
       <c r="D44" t="n">
-        <v>1.049008416937481</v>
+        <v>1.000926366411471</v>
       </c>
     </row>
     <row r="45">
@@ -1136,10 +1136,10 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>2.129176810607219</v>
+        <v>1.745006137982126</v>
       </c>
       <c r="D45" t="n">
-        <v>1.029786054152452</v>
+        <v>1.001094013230701</v>
       </c>
     </row>
     <row r="46">
@@ -1152,10 +1152,10 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>2.097301376371893</v>
+        <v>1.065902789347106</v>
       </c>
       <c r="D46" t="n">
-        <v>1.086092081965878</v>
+        <v>1.006620075368187</v>
       </c>
     </row>
     <row r="47">
@@ -1168,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>2.097301376371893</v>
+        <v>1.782719819467118</v>
       </c>
       <c r="D47" t="n">
-        <v>1.276553352004134</v>
+        <v>1.007917438363312</v>
       </c>
     </row>
     <row r="48">
@@ -1184,10 +1184,10 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>2.097301376371893</v>
+        <v>2.159098479130408</v>
       </c>
       <c r="D48" t="n">
-        <v>2.744553245101073</v>
+        <v>2.837546370724542</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hospital_summary.xlsx
+++ b/outputs/hospital_summary.xlsx
@@ -451,7 +451,7 @@
         <v>2.177682639126641</v>
       </c>
       <c r="D2" t="n">
-        <v>1.071061827129748</v>
+        <v>1.031305052885321</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         <v>2.195428426552186</v>
       </c>
       <c r="D3" t="n">
-        <v>1.044501294258234</v>
+        <v>1.029994289764539</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +483,7 @@
         <v>2.218541825787641</v>
       </c>
       <c r="D4" t="n">
-        <v>1.374854953355303</v>
+        <v>1.134050345396733</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         <v>2.278616178635162</v>
       </c>
       <c r="D5" t="n">
-        <v>1.090523476197044</v>
+        <v>1.074765134529771</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         <v>2.238810739616622</v>
       </c>
       <c r="D6" t="n">
-        <v>1.060812748256447</v>
+        <v>1.039853868717295</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>2.190493328687032</v>
       </c>
       <c r="D7" t="n">
-        <v>1.032544991596828</v>
+        <v>1.022888214483426</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         <v>2.107468634740377</v>
       </c>
       <c r="D8" t="n">
-        <v>1.019508968145117</v>
+        <v>1.010457469977934</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>2.194401309340316</v>
       </c>
       <c r="D9" t="n">
-        <v>1.039482959585712</v>
+        <v>1.049378842262576</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +579,7 @@
         <v>2.127220584661621</v>
       </c>
       <c r="D10" t="n">
-        <v>1.041891539182229</v>
+        <v>1.018795409665965</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +595,7 @@
         <v>2.31304270891115</v>
       </c>
       <c r="D11" t="n">
-        <v>2.882911465181623</v>
+        <v>2.8872924720869</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         <v>2.147167199272698</v>
       </c>
       <c r="D12" t="n">
-        <v>1.054873544966977</v>
+        <v>1.02250281660522</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +627,7 @@
         <v>2.203381001286713</v>
       </c>
       <c r="D13" t="n">
-        <v>1.034065521272477</v>
+        <v>1.027277192176545</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +643,7 @@
         <v>2.173098848687933</v>
       </c>
       <c r="D14" t="n">
-        <v>1.036553796011563</v>
+        <v>1.01908929598687</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         <v>2.107121097563563</v>
       </c>
       <c r="D15" t="n">
-        <v>1.014988050878614</v>
+        <v>1.00934628127756</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         <v>1.814894809625688</v>
       </c>
       <c r="D16" t="n">
-        <v>1.001827626050436</v>
+        <v>1.003251831044649</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +691,7 @@
         <v>1.7141611724479</v>
       </c>
       <c r="D17" t="n">
-        <v>1.00210770601287</v>
+        <v>1.001535352972062</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +707,7 @@
         <v>1.626883503077782</v>
       </c>
       <c r="D18" t="n">
-        <v>1.00075718223853</v>
+        <v>1.000549998844653</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         <v>1.954744738438457</v>
       </c>
       <c r="D19" t="n">
-        <v>1.007149157155526</v>
+        <v>1.017547590005717</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +739,7 @@
         <v>1.575073186713787</v>
       </c>
       <c r="D20" t="n">
-        <v>1.002220938875395</v>
+        <v>1.002316316400997</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +755,7 @@
         <v>1.391370579658687</v>
       </c>
       <c r="D21" t="n">
-        <v>1.00091003512941</v>
+        <v>1.00014307445013</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +771,7 @@
         <v>1.583365492283237</v>
       </c>
       <c r="D22" t="n">
-        <v>1.00992368922174</v>
+        <v>1.001056567375081</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         <v>1.580578806924005</v>
       </c>
       <c r="D23" t="n">
-        <v>1.006505776717569</v>
+        <v>1.004345002508984</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +803,7 @@
         <v>1.585476855519401</v>
       </c>
       <c r="D24" t="n">
-        <v>1.005087488100988</v>
+        <v>1.00341117780849</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +819,7 @@
         <v>2.20509018218745</v>
       </c>
       <c r="D25" t="n">
-        <v>2.315267798700703</v>
+        <v>2.270605130183447</v>
       </c>
     </row>
     <row r="26">
@@ -835,7 +835,7 @@
         <v>2.091743962646496</v>
       </c>
       <c r="D26" t="n">
-        <v>1.048059596489599</v>
+        <v>1.046870631470516</v>
       </c>
     </row>
     <row r="27">
@@ -851,7 +851,7 @@
         <v>2.04837127749825</v>
       </c>
       <c r="D27" t="n">
-        <v>1.05166379701486</v>
+        <v>1.054544029974505</v>
       </c>
     </row>
     <row r="28">
@@ -867,7 +867,7 @@
         <v>2.015814089069948</v>
       </c>
       <c r="D28" t="n">
-        <v>1.020600311144518</v>
+        <v>1.049898181321987</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +883,7 @@
         <v>2.045293897884996</v>
       </c>
       <c r="D29" t="n">
-        <v>2.564026113922534</v>
+        <v>2.510167507472313</v>
       </c>
     </row>
     <row r="30">
@@ -899,7 +899,7 @@
         <v>2.013159770003356</v>
       </c>
       <c r="D30" t="n">
-        <v>2.428267768300765</v>
+        <v>2.157511569917461</v>
       </c>
     </row>
     <row r="31">
@@ -915,7 +915,7 @@
         <v>1.987378255294497</v>
       </c>
       <c r="D31" t="n">
-        <v>1.019161279942785</v>
+        <v>1.046446877769747</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +931,7 @@
         <v>1.934547685258584</v>
       </c>
       <c r="D32" t="n">
-        <v>1.00639876927893</v>
+        <v>1.012795897252183</v>
       </c>
     </row>
     <row r="33">
@@ -947,7 +947,7 @@
         <v>1.971456457640082</v>
       </c>
       <c r="D33" t="n">
-        <v>1.006434709134189</v>
+        <v>1.007105978277511</v>
       </c>
     </row>
     <row r="34">
@@ -963,7 +963,7 @@
         <v>2.205926716882059</v>
       </c>
       <c r="D34" t="n">
-        <v>1.062205042722092</v>
+        <v>1.041218477502077</v>
       </c>
     </row>
     <row r="35">
@@ -979,7 +979,7 @@
         <v>2.256166084887665</v>
       </c>
       <c r="D35" t="n">
-        <v>1.052992138865038</v>
+        <v>1.049835138266607</v>
       </c>
     </row>
     <row r="36">
@@ -995,7 +995,7 @@
         <v>2.2757784853328</v>
       </c>
       <c r="D36" t="n">
-        <v>1.058271182087071</v>
+        <v>1.086496754071889</v>
       </c>
     </row>
     <row r="37">
@@ -1011,7 +1011,7 @@
         <v>2.321728551842823</v>
       </c>
       <c r="D37" t="n">
-        <v>2.830131163104121</v>
+        <v>2.781355463937098</v>
       </c>
     </row>
     <row r="38">
@@ -1027,7 +1027,7 @@
         <v>2.079677061441526</v>
       </c>
       <c r="D38" t="n">
-        <v>1.149784091983938</v>
+        <v>1.029546024069546</v>
       </c>
     </row>
     <row r="39">
@@ -1043,7 +1043,7 @@
         <v>1.100411368044227</v>
       </c>
       <c r="D39" t="n">
-        <v>1.000592876951873</v>
+        <v>1.00085787381333</v>
       </c>
     </row>
     <row r="40">
@@ -1059,7 +1059,7 @@
         <v>1.713370735726198</v>
       </c>
       <c r="D40" t="n">
-        <v>1.070004670929269</v>
+        <v>1.277478133606368</v>
       </c>
     </row>
     <row r="41">
@@ -1075,7 +1075,7 @@
         <v>1.403786503688199</v>
       </c>
       <c r="D41" t="n">
-        <v>1.006800811502852</v>
+        <v>1.000269216587124</v>
       </c>
     </row>
     <row r="42">
@@ -1091,7 +1091,7 @@
         <v>1.039299999265725</v>
       </c>
       <c r="D42" t="n">
-        <v>1.000754833446681</v>
+        <v>1.000116598877237</v>
       </c>
     </row>
     <row r="43">
@@ -1107,7 +1107,7 @@
         <v>1.3385364430736</v>
       </c>
       <c r="D43" t="n">
-        <v>1.007827866504861</v>
+        <v>1.05709269145438</v>
       </c>
     </row>
     <row r="44">
@@ -1123,7 +1123,7 @@
         <v>1.218705354107325</v>
       </c>
       <c r="D44" t="n">
-        <v>1.000926366411471</v>
+        <v>1.005070751767151</v>
       </c>
     </row>
     <row r="45">
@@ -1139,7 +1139,7 @@
         <v>1.745006137982126</v>
       </c>
       <c r="D45" t="n">
-        <v>1.001094013230701</v>
+        <v>1.003013495145151</v>
       </c>
     </row>
     <row r="46">
@@ -1155,7 +1155,7 @@
         <v>1.065902789347106</v>
       </c>
       <c r="D46" t="n">
-        <v>1.006620075368187</v>
+        <v>1.000285620153248</v>
       </c>
     </row>
     <row r="47">
@@ -1171,7 +1171,7 @@
         <v>1.782719819467118</v>
       </c>
       <c r="D47" t="n">
-        <v>1.007917438363312</v>
+        <v>1.935193663659678</v>
       </c>
     </row>
     <row r="48">
@@ -1187,7 +1187,7 @@
         <v>2.159098479130408</v>
       </c>
       <c r="D48" t="n">
-        <v>2.837546370724542</v>
+        <v>2.869677165902385</v>
       </c>
     </row>
   </sheetData>
